--- a/ig/DM-AVRIL-2026/CodeSystem-terminologie-cisis.xlsx
+++ b/ig/DM-AVRIL-2026/CodeSystem-terminologie-cisis.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4879" uniqueCount="3255">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4882" uniqueCount="3257">
   <si>
     <t>Property</t>
   </si>
@@ -37,7 +37,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>202603110000</t>
+    <t>202604200000</t>
   </si>
   <si>
     <t>Name</t>
@@ -67,7 +67,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-11T14:52:01-00:00</t>
+    <t>2026-04-20T11:06:51-00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -8561,6 +8561,12 @@
   </si>
   <si>
     <t>Questionnaire Mon Bilan Prévention 70-75 ans</t>
+  </si>
+  <si>
+    <t>MED-1350</t>
+  </si>
+  <si>
+    <t>Entrées/sorties hydro-électrolytiques</t>
   </si>
   <si>
     <t>ORG-001</t>
@@ -10180,7 +10186,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:D1606"/>
+  <dimension ref="A1:D1607"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -29457,6 +29463,18 @@
       </c>
       <c r="D1606" s="2"/>
     </row>
+    <row r="1607">
+      <c r="A1607" t="s" s="2">
+        <v>57</v>
+      </c>
+      <c r="B1607" t="s" s="2">
+        <v>3255</v>
+      </c>
+      <c r="C1607" t="s" s="2">
+        <v>3256</v>
+      </c>
+      <c r="D1607" s="2"/>
+    </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>
